--- a/artfynd/A 34210-2025 artfynd.xlsx
+++ b/artfynd/A 34210-2025 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>127121029</v>
       </c>
       <c r="B3" t="n">
-        <v>95964</v>
+        <v>96039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34210-2025 artfynd.xlsx
+++ b/artfynd/A 34210-2025 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>127121029</v>
       </c>
       <c r="B3" t="n">
-        <v>96039</v>
+        <v>96045</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34210-2025 artfynd.xlsx
+++ b/artfynd/A 34210-2025 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>127121029</v>
       </c>
       <c r="B3" t="n">
-        <v>96045</v>
+        <v>96046</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34210-2025 artfynd.xlsx
+++ b/artfynd/A 34210-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127121025</v>
       </c>
       <c r="B2" t="n">
-        <v>58027</v>
+        <v>58031</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>127121029</v>
       </c>
       <c r="B3" t="n">
-        <v>96046</v>
+        <v>96050</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>127121022</v>
       </c>
       <c r="B4" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34210-2025 artfynd.xlsx
+++ b/artfynd/A 34210-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127121025</v>
       </c>
       <c r="B2" t="n">
-        <v>58031</v>
+        <v>58033</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>127121029</v>
       </c>
       <c r="B3" t="n">
-        <v>96050</v>
+        <v>96052</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>127121022</v>
       </c>
       <c r="B4" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34210-2025 artfynd.xlsx
+++ b/artfynd/A 34210-2025 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>127121029</v>
       </c>
       <c r="B3" t="n">
-        <v>96052</v>
+        <v>96058</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34210-2025 artfynd.xlsx
+++ b/artfynd/A 34210-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127121025</v>
       </c>
       <c r="B2" t="n">
-        <v>58033</v>
+        <v>58036</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>127121029</v>
       </c>
       <c r="B3" t="n">
-        <v>96058</v>
+        <v>96061</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>127121022</v>
       </c>
       <c r="B4" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34210-2025 artfynd.xlsx
+++ b/artfynd/A 34210-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127121025</v>
       </c>
       <c r="B2" t="n">
-        <v>58036</v>
+        <v>58042</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>127121029</v>
       </c>
       <c r="B3" t="n">
-        <v>96061</v>
+        <v>96069</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>127121022</v>
       </c>
       <c r="B4" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34210-2025 artfynd.xlsx
+++ b/artfynd/A 34210-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127121025</v>
       </c>
       <c r="B2" t="n">
-        <v>58042</v>
+        <v>58027</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>127121029</v>
       </c>
       <c r="B3" t="n">
-        <v>96069</v>
+        <v>96039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>127121022</v>
       </c>
       <c r="B4" t="n">
-        <v>57669</v>
+        <v>57654</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
